--- a/hall_of_fame.xlsx
+++ b/hall_of_fame.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\blocks_hall_of_fame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD8320B-1E81-4E12-832D-CB1079AB8D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA94C245-5EBF-462A-8B30-5D04CAFE94F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4305" yWindow="960" windowWidth="21600" windowHeight="11250" xr2:uid="{78BDC05C-5D94-4C11-95C7-B3A2824BBBF0}"/>
+    <workbookView xWindow="4080" yWindow="1740" windowWidth="21600" windowHeight="11250" xr2:uid="{78BDC05C-5D94-4C11-95C7-B3A2824BBBF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="50">
   <si>
     <t>CollectorName</t>
   </si>
@@ -178,6 +178,12 @@
   </si>
   <si>
     <t>ananhaque775606</t>
+  </si>
+  <si>
+    <t>Jishan Sheikh</t>
+  </si>
+  <si>
+    <t>jishan134914</t>
   </si>
 </sst>
 </file>
@@ -573,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6460CF-3B38-4B58-B187-39367883653E}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -1023,7 +1029,7 @@
         <v>7</v>
       </c>
       <c r="H19" s="6">
-        <v>45661</v>
+        <v>46026</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1046,7 +1052,30 @@
         <v>7</v>
       </c>
       <c r="H20" s="6">
-        <v>45690</v>
+        <v>46055</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="6">
+        <v>46063</v>
       </c>
     </row>
   </sheetData>

--- a/hall_of_fame.xlsx
+++ b/hall_of_fame.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\blocks_hall_of_fame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA94C245-5EBF-462A-8B30-5D04CAFE94F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EE4605-9697-4D60-8BF3-4EDAE54C13E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="1740" windowWidth="21600" windowHeight="11250" xr2:uid="{78BDC05C-5D94-4C11-95C7-B3A2824BBBF0}"/>
+    <workbookView xWindow="4290" yWindow="1605" windowWidth="21600" windowHeight="11250" xr2:uid="{78BDC05C-5D94-4C11-95C7-B3A2824BBBF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="52">
   <si>
     <t>CollectorName</t>
   </si>
@@ -184,6 +184,12 @@
   </si>
   <si>
     <t>jishan134914</t>
+  </si>
+  <si>
+    <t>Ezeey420525</t>
+  </si>
+  <si>
+    <t>Abdullah Al Rahi</t>
   </si>
 </sst>
 </file>
@@ -245,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -265,6 +271,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,12 +588,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6460CF-3B38-4B58-B187-39367883653E}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" style="9" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" style="4" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
@@ -625,7 +634,7 @@
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="9">
         <v>0</v>
       </c>
       <c r="D2" s="4">
@@ -648,7 +657,7 @@
       <c r="B3" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="9">
         <v>0</v>
       </c>
       <c r="D3" s="4">
@@ -671,7 +680,7 @@
       <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="9">
         <v>0</v>
       </c>
       <c r="D4" s="4">
@@ -694,7 +703,7 @@
       <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="9">
         <v>0</v>
       </c>
       <c r="D5" s="4">
@@ -717,7 +726,7 @@
       <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="9">
         <v>0</v>
       </c>
       <c r="D6" s="4">
@@ -740,7 +749,7 @@
       <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="9">
         <v>0</v>
       </c>
       <c r="D7" s="4">
@@ -763,7 +772,7 @@
       <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="9">
         <v>21</v>
       </c>
       <c r="D8" s="4">
@@ -786,7 +795,7 @@
       <c r="B9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="9">
         <v>12</v>
       </c>
       <c r="D9" s="4">
@@ -809,7 +818,7 @@
       <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="9">
         <v>1</v>
       </c>
       <c r="D10" s="4">
@@ -832,7 +841,7 @@
       <c r="B11" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="9">
         <v>0</v>
       </c>
       <c r="D11" s="4">
@@ -855,7 +864,7 @@
       <c r="B12" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="9">
         <v>0</v>
       </c>
       <c r="D12" s="4">
@@ -878,7 +887,7 @@
       <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="9">
         <v>0</v>
       </c>
       <c r="D13" s="4">
@@ -901,7 +910,7 @@
       <c r="B14" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="9">
         <v>0</v>
       </c>
       <c r="D14" s="4">
@@ -924,7 +933,7 @@
       <c r="B15" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="9">
         <v>21</v>
       </c>
       <c r="D15" s="4">
@@ -947,7 +956,7 @@
       <c r="B16" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="9">
         <v>0</v>
       </c>
       <c r="D16" s="4">
@@ -970,7 +979,7 @@
       <c r="B17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="9">
         <v>1</v>
       </c>
       <c r="D17" s="4">
@@ -993,7 +1002,7 @@
       <c r="B18" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="9">
         <v>0</v>
       </c>
       <c r="D18" s="4">
@@ -1016,7 +1025,7 @@
       <c r="B19" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="9">
         <v>0</v>
       </c>
       <c r="D19" s="4">
@@ -1039,7 +1048,7 @@
       <c r="B20" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="9">
         <v>0</v>
       </c>
       <c r="D20" s="4">
@@ -1062,7 +1071,7 @@
       <c r="B21" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="9">
         <v>0</v>
       </c>
       <c r="D21" s="4">
@@ -1076,6 +1085,30 @@
       </c>
       <c r="H21" s="6">
         <v>46063</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="9">
+        <v>37</v>
+      </c>
+      <c r="D22" s="4">
+        <v>75</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="6">
+        <v>46102</v>
       </c>
     </row>
   </sheetData>
